--- a/saved_mandates/master_mandate.xlsx
+++ b/saved_mandates/master_mandate.xlsx
@@ -616,12 +616,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Government of Canada 3.25% Sep 2026</t>
+          <t>iShares 1-5 Year Laddered Government Bond Index ETF</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>CAN325-26</t>
+          <t>CLF.TO</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -652,12 +652,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Guardian Investment Grade Corporate Bond ETF</t>
+          <t>BMO Aggregate Bond Index ETF</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>CIGB.TO</t>
+          <t>ZAG.TO</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
@@ -724,12 +724,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Canso Corporate Bond Fund</t>
+          <t>iShares Canadian Corporate Bond Index ETF</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>CANSO-CB (Fund)</t>
+          <t>XCB.TO</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
@@ -1051,6 +1051,7 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
@@ -1195,12 +1196,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Government of Canada 3.25% Sep 2026</t>
+          <t>iShares 1-5 Year Laddered Government Bond Index ETF</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>CAN325-26</t>
+          <t>CLF.TO</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -1231,12 +1232,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Guardian Investment Grade Corporate Bond ETF</t>
+          <t>BMO Aggregate Bond Index ETF</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>CIGB.TO</t>
+          <t>ZAG.TO</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
@@ -1303,12 +1304,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Canso Corporate Bond Fund</t>
+          <t>iShares Canadian Corporate Bond Index ETF</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>CANSO-CB (Fund)</t>
+          <t>XCB.TO</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
@@ -1918,6 +1919,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
@@ -2062,12 +2064,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Government of Canada 3.25% Sep 2028</t>
+          <t>iShares 1-5 Year Laddered Government Bond Index ETF</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>CAN325-28</t>
+          <t>CLF.TO</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -2098,12 +2100,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Guardian Investment Grade Corporate Bond ETF</t>
+          <t>BMO Aggregate Bond Index ETF</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>CIGB.TO</t>
+          <t>ZAG.TO</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
@@ -2821,6 +2823,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
@@ -2837,8 +2840,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -3688,6 +3691,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
